--- a/artfynd/A 43250-2023 artfynd.xlsx
+++ b/artfynd/A 43250-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 43250-2023 artfynd.xlsx
+++ b/artfynd/A 43250-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>103755751</v>
       </c>
       <c r="B2" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>767752.9347872233</v>
+        <v>767753</v>
       </c>
       <c r="R2" t="n">
-        <v>7158614.911648265</v>
+        <v>7158615</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,19 +746,9 @@
           <t>2022-09-22</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-09-22</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -796,54 +781,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104330349</v>
+        <v>117521465</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lidberget, Vb</t>
+          <t>Notsjöbäcken, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>767789.7356314505</v>
+        <v>767721</v>
       </c>
       <c r="R3" t="n">
-        <v>7158606.434931668</v>
+        <v>7158487</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,22 +849,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-10-15</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-10-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,27 +870,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Sven Bengtsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Sven Bengtsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104330376</v>
+        <v>104330349</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -957,10 +921,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>767788.5503316554</v>
+        <v>767790</v>
       </c>
       <c r="R4" t="n">
-        <v>7158486.583978255</v>
+        <v>7158607</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,19 +954,9 @@
           <t>2022-10-15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-10-15</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,6 +981,108 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>104330376</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Lidberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>767788</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7158487</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-10-15</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-10-15</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 43250-2023 artfynd.xlsx
+++ b/artfynd/A 43250-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103755751</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117521465</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -981,6 +996,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104330349</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1083,8 +1103,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104330376</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>